--- a/1_assemble_dataset/time_use/surveys/codebooks/India_Categorization_Codes.xlsx
+++ b/1_assemble_dataset/time_use/surveys/codebooks/India_Categorization_Codes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11109"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/egreinger/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/project/cil/home_dirs/egrenier/repos/labor-code-release-2020/1_assemble_dataset/time_use/surveys/codebooks/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17CCB245-B451-7B41-9475-CFF387CB0B81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC3C54AB-AE2C-564A-B694-ED34159FDD24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="500" windowWidth="38400" windowHeight="21100" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="20160" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cat" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1192" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1181" uniqueCount="214">
   <si>
     <t>Ploughing, preparing land, cleaning of land</t>
   </si>
@@ -671,13 +671,13 @@
     <t>Agriculture</t>
   </si>
   <si>
-    <t>high risk????</t>
-  </si>
-  <si>
     <t>Manuf</t>
   </si>
   <si>
     <t>Mining + construction</t>
+  </si>
+  <si>
+    <t>low risk</t>
   </si>
 </sst>
 </file>
@@ -925,11 +925,11 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
@@ -1287,9 +1287,8 @@
     <col min="7" max="7" width="14.1640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="16" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="35.5" customWidth="1"/>
-    <col min="11" max="11" width="22.6640625" style="41" customWidth="1"/>
-    <col min="12" max="12" width="25" style="41" customWidth="1"/>
-    <col min="13" max="16384" width="10.83203125" style="41"/>
+    <col min="11" max="11" width="22.6640625" customWidth="1"/>
+    <col min="12" max="12" width="25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" s="2" customFormat="1">
@@ -1348,7 +1347,7 @@
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
     </row>
-    <row r="5" spans="1:14" customFormat="1" ht="34">
+    <row r="5" spans="1:14" ht="34">
       <c r="A5" s="3" t="s">
         <v>151</v>
       </c>
@@ -1529,8 +1528,8 @@
       <c r="L9" s="13" t="s">
         <v>210</v>
       </c>
-      <c r="M9" s="42"/>
-      <c r="N9" s="43"/>
+      <c r="M9" s="41"/>
+      <c r="N9" s="42"/>
     </row>
     <row r="10" spans="1:14" ht="34">
       <c r="A10" s="13">
@@ -1669,11 +1668,10 @@
         <v>183</v>
       </c>
       <c r="J13" s="13"/>
-      <c r="K13" s="13" t="s">
-        <v>209</v>
-      </c>
-      <c r="L13" s="13" t="s">
-        <v>210</v>
+      <c r="K13" s="43"/>
+      <c r="L13" s="43"/>
+      <c r="M13" s="45" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="34">
@@ -1786,7 +1784,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="17">
+    <row r="17" spans="1:13" ht="17">
       <c r="A17" s="13">
         <v>123</v>
       </c>
@@ -1822,7 +1820,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="17">
+    <row r="18" spans="1:13" ht="17">
       <c r="A18" s="13">
         <v>124</v>
       </c>
@@ -1858,7 +1856,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="17">
+    <row r="19" spans="1:13" ht="17">
       <c r="A19" s="13">
         <v>125</v>
       </c>
@@ -1894,7 +1892,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="17">
+    <row r="20" spans="1:13" ht="17">
       <c r="A20" s="13">
         <v>126</v>
       </c>
@@ -1930,7 +1928,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="17">
+    <row r="21" spans="1:13" ht="17">
       <c r="A21" s="13">
         <v>127</v>
       </c>
@@ -1966,7 +1964,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="17">
+    <row r="22" spans="1:13" ht="17">
       <c r="A22" s="13">
         <v>128</v>
       </c>
@@ -1995,12 +1993,13 @@
         <v>183</v>
       </c>
       <c r="J22" s="13"/>
-      <c r="K22" s="13" t="s">
-        <v>209</v>
-      </c>
-      <c r="L22" s="44"/>
-    </row>
-    <row r="23" spans="1:12" ht="17">
+      <c r="K22" s="43"/>
+      <c r="L22" s="43"/>
+      <c r="M22" s="45" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="17">
       <c r="A23" s="21">
         <v>129</v>
       </c>
@@ -2038,7 +2037,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="34">
+    <row r="24" spans="1:13" ht="34">
       <c r="A24" s="13">
         <v>131</v>
       </c>
@@ -2074,7 +2073,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="34">
+    <row r="25" spans="1:13" ht="34">
       <c r="A25" s="13">
         <v>132</v>
       </c>
@@ -2110,7 +2109,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="34">
+    <row r="26" spans="1:13" ht="34">
       <c r="A26" s="13">
         <v>133</v>
       </c>
@@ -2146,7 +2145,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="34">
+    <row r="27" spans="1:13" ht="34">
       <c r="A27" s="13">
         <v>134</v>
       </c>
@@ -2182,7 +2181,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="34">
+    <row r="28" spans="1:13" ht="34">
       <c r="A28" s="13">
         <v>135</v>
       </c>
@@ -2218,7 +2217,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="34">
+    <row r="29" spans="1:13" ht="34">
       <c r="A29" s="13">
         <v>136</v>
       </c>
@@ -2247,12 +2246,13 @@
         <v>183</v>
       </c>
       <c r="J29" s="13"/>
-      <c r="K29" s="44" t="s">
-        <v>211</v>
-      </c>
-      <c r="L29" s="44"/>
-    </row>
-    <row r="30" spans="1:12" ht="34">
+      <c r="K29" s="45"/>
+      <c r="L29" s="45"/>
+      <c r="M29" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="34">
       <c r="A30" s="13">
         <v>137</v>
       </c>
@@ -2288,7 +2288,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="34">
+    <row r="31" spans="1:13" ht="34">
       <c r="A31" s="13">
         <v>138</v>
       </c>
@@ -2317,12 +2317,13 @@
         <v>183</v>
       </c>
       <c r="J31" s="13"/>
-      <c r="K31" s="13" t="s">
-        <v>209</v>
-      </c>
-      <c r="L31" s="44"/>
-    </row>
-    <row r="32" spans="1:12" ht="34">
+      <c r="K31" s="43"/>
+      <c r="L31" s="43"/>
+      <c r="M31" s="45" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="34">
       <c r="A32" s="21">
         <v>139</v>
       </c>
@@ -2641,12 +2642,8 @@
         <v>183</v>
       </c>
       <c r="J40" s="13"/>
-      <c r="K40" s="44" t="s">
-        <v>209</v>
-      </c>
-      <c r="L40" s="44" t="s">
-        <v>210</v>
-      </c>
+      <c r="K40" s="45"/>
+      <c r="L40" s="45"/>
     </row>
     <row r="41" spans="1:12" ht="51">
       <c r="A41" s="13">
@@ -2754,8 +2751,8 @@
       <c r="K43" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="L43" s="45" t="s">
-        <v>212</v>
+      <c r="L43" s="44" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="44" spans="1:12" ht="17">
@@ -2790,8 +2787,8 @@
       <c r="K44" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="L44" s="45" t="s">
-        <v>212</v>
+      <c r="L44" s="44" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="45" spans="1:12" ht="17">
@@ -2826,8 +2823,8 @@
       <c r="K45" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="L45" s="45" t="s">
-        <v>212</v>
+      <c r="L45" s="44" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="46" spans="1:12" ht="17">
@@ -2862,8 +2859,8 @@
       <c r="K46" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="L46" s="45" t="s">
-        <v>212</v>
+      <c r="L46" s="44" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="47" spans="1:12" ht="17">
@@ -2898,8 +2895,8 @@
       <c r="K47" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="L47" s="45" t="s">
-        <v>212</v>
+      <c r="L47" s="44" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="48" spans="1:12" ht="17">
@@ -2931,12 +2928,8 @@
         <v>183</v>
       </c>
       <c r="J48" s="13"/>
-      <c r="K48" s="44" t="s">
-        <v>209</v>
-      </c>
-      <c r="L48" s="44" t="s">
-        <v>212</v>
-      </c>
+      <c r="K48" s="45"/>
+      <c r="L48" s="45"/>
     </row>
     <row r="49" spans="1:12" ht="17">
       <c r="A49" s="21">
@@ -2972,8 +2965,8 @@
       <c r="K49" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="L49" s="45" t="s">
-        <v>212</v>
+      <c r="L49" s="44" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="50" spans="1:12" ht="34">
@@ -3009,7 +3002,7 @@
         <v>209</v>
       </c>
       <c r="L50" s="13" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="51" spans="1:12" ht="34">
@@ -3045,7 +3038,7 @@
         <v>209</v>
       </c>
       <c r="L51" s="13" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="52" spans="1:12" ht="34">
@@ -3081,7 +3074,7 @@
         <v>209</v>
       </c>
       <c r="L52" s="13" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="53" spans="1:12" ht="34">
@@ -3117,7 +3110,7 @@
         <v>209</v>
       </c>
       <c r="L53" s="13" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="54" spans="1:12" ht="34">
@@ -3152,8 +3145,8 @@
       <c r="K54" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="L54" s="13" t="s">
-        <v>213</v>
+      <c r="L54" s="44" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="55" spans="1:12" ht="34">
@@ -3189,7 +3182,7 @@
         <v>209</v>
       </c>
       <c r="L55" s="13" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="56" spans="1:12" ht="34">
@@ -3225,7 +3218,7 @@
         <v>209</v>
       </c>
       <c r="L56" s="13" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="57" spans="1:12" ht="34">
@@ -3257,12 +3250,8 @@
         <v>183</v>
       </c>
       <c r="J57" s="13"/>
-      <c r="K57" s="44" t="s">
-        <v>209</v>
-      </c>
-      <c r="L57" s="44" t="s">
-        <v>213</v>
-      </c>
+      <c r="K57" s="45"/>
+      <c r="L57" s="45"/>
     </row>
     <row r="58" spans="1:12" ht="34">
       <c r="A58" s="21">
@@ -3299,7 +3288,7 @@
         <v>209</v>
       </c>
       <c r="L58" s="13" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="59" spans="1:12" ht="34">
@@ -3335,7 +3324,7 @@
         <v>209</v>
       </c>
       <c r="L59" s="13" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="60" spans="1:12" ht="17">
@@ -3371,7 +3360,7 @@
         <v>209</v>
       </c>
       <c r="L60" s="13" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="61" spans="1:12" ht="17">
@@ -3407,7 +3396,7 @@
         <v>209</v>
       </c>
       <c r="L61" s="13" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="62" spans="1:12" ht="17">
@@ -3443,7 +3432,7 @@
         <v>209</v>
       </c>
       <c r="L62" s="13" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="63" spans="1:12" ht="17">
@@ -3479,7 +3468,7 @@
         <v>209</v>
       </c>
       <c r="L63" s="13" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="64" spans="1:12" ht="17">
@@ -3511,12 +3500,8 @@
         <v>183</v>
       </c>
       <c r="J64" s="13"/>
-      <c r="K64" s="44" t="s">
-        <v>209</v>
-      </c>
-      <c r="L64" s="44" t="s">
-        <v>213</v>
-      </c>
+      <c r="K64" s="45"/>
+      <c r="L64" s="45"/>
     </row>
     <row r="65" spans="1:12" ht="17">
       <c r="A65" s="21">
@@ -3553,7 +3538,7 @@
         <v>209</v>
       </c>
       <c r="L65" s="13" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="66" spans="1:12" ht="34">
@@ -3588,8 +3573,8 @@
       <c r="K66" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="L66" s="45" t="s">
-        <v>212</v>
+      <c r="L66" s="44" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="67" spans="1:12" ht="17">
@@ -3624,8 +3609,8 @@
       <c r="K67" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="L67" s="45" t="s">
-        <v>212</v>
+      <c r="L67" s="44" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="68" spans="1:12" ht="34">
@@ -3660,8 +3645,8 @@
       <c r="K68" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="L68" s="45" t="s">
-        <v>212</v>
+      <c r="L68" s="44" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="69" spans="1:12" ht="34">
@@ -3696,8 +3681,8 @@
       <c r="K69" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="L69" s="45" t="s">
-        <v>212</v>
+      <c r="L69" s="44" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="70" spans="1:12" ht="17">
@@ -3732,8 +3717,8 @@
       <c r="K70" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="L70" s="45" t="s">
-        <v>212</v>
+      <c r="L70" s="44" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="71" spans="1:12" ht="17">
@@ -3768,8 +3753,8 @@
       <c r="K71" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="L71" s="45" t="s">
-        <v>212</v>
+      <c r="L71" s="44" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="72" spans="1:12" ht="51">
@@ -3804,8 +3789,8 @@
       <c r="K72" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="L72" s="45" t="s">
-        <v>212</v>
+      <c r="L72" s="44" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="73" spans="1:12" ht="17">
@@ -3837,12 +3822,8 @@
         <v>183</v>
       </c>
       <c r="J73" s="13"/>
-      <c r="K73" s="44" t="s">
-        <v>209</v>
-      </c>
-      <c r="L73" s="44" t="s">
-        <v>212</v>
-      </c>
+      <c r="K73" s="45"/>
+      <c r="L73" s="45"/>
     </row>
     <row r="74" spans="1:12" ht="17">
       <c r="A74" s="21">
@@ -3878,8 +3859,8 @@
       <c r="K74" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="L74" s="45" t="s">
-        <v>212</v>
+      <c r="L74" s="44" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="75" spans="1:12" ht="34">
@@ -3941,11 +3922,11 @@
         <v>183</v>
       </c>
       <c r="J76" s="13"/>
-      <c r="K76" s="44" t="s">
+      <c r="K76" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="L76" s="44" t="s">
         <v>211</v>
-      </c>
-      <c r="L76" s="45" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="77" spans="1:12" ht="17">
@@ -3980,8 +3961,8 @@
       <c r="K77" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="L77" s="45" t="s">
-        <v>212</v>
+      <c r="L77" s="44" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="78" spans="1:12" ht="17">
@@ -4016,8 +3997,8 @@
       <c r="K78" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="L78" s="45" t="s">
-        <v>212</v>
+      <c r="L78" s="44" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="79" spans="1:12" ht="17">
@@ -4052,8 +4033,8 @@
       <c r="K79" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="L79" s="45" t="s">
-        <v>212</v>
+      <c r="L79" s="44" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="80" spans="1:12" ht="17">
@@ -4088,8 +4069,8 @@
       <c r="K80" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="L80" s="45" t="s">
-        <v>212</v>
+      <c r="L80" s="44" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="81" spans="1:12" ht="17">
@@ -4126,8 +4107,8 @@
       <c r="K81" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="L81" s="45" t="s">
-        <v>212</v>
+      <c r="L81" s="44" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="82" spans="1:12" ht="17">
@@ -4312,8 +4293,8 @@
       <c r="K87" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="L87" s="45" t="s">
-        <v>212</v>
+      <c r="L87" s="44" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="88" spans="1:12" ht="17">
@@ -6478,7 +6459,7 @@
       </c>
       <c r="J158" s="33"/>
     </row>
-    <row r="159" spans="1:10" ht="34">
+    <row r="159" spans="1:10" ht="51">
       <c r="A159" s="29">
         <v>982</v>
       </c>
